--- a/basedatos_partidas/salida/descompuestos/CT-09-01-060.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-09-01-060.xlsx
@@ -539,10 +539,10 @@
         <v>1.45</v>
       </c>
       <c r="G10" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="H10" t="n">
-        <v>6.09</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="H11" t="n">
-        <v>4.34</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="12">
@@ -591,10 +591,10 @@
         <v>0.85</v>
       </c>
       <c r="G12" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="H12" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="13">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>14.79</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="16">
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>22.98</v>
+        <v>26.7</v>
       </c>
       <c r="H26" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="27">
@@ -873,7 +873,7 @@
       </c>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n">
-        <v>23.21</v>
+        <v>26.97</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-09-01-060.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-09-01-060.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 09 Cielos rasos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Yeso laminado continuo</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
